--- a/Lab_4/data/partB/param_optimization_process/v150_k10_s150_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v150_k10_s150_results.xlsx
@@ -518,28 +518,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -548,19 +548,19 @@
         <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -573,16 +573,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -591,25 +591,25 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
         <v>9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -698,25 +698,25 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -726,49 +726,49 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
         <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
+        <v>17</v>
+      </c>
+      <c r="N6" t="n">
         <v>12</v>
       </c>
-      <c r="N6" t="n">
-        <v>4</v>
-      </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -790,37 +790,37 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
         <v>8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -842,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -860,19 +860,19 @@
         <v>11</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -891,40 +891,40 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>12</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -958,19 +958,19 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -1062,19 +1062,19 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1096,25 +1096,25 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
@@ -1123,13 +1123,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -1154,19 +1154,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1175,16 +1175,16 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -1255,40 +1255,40 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
         <v>6</v>
       </c>
-      <c r="F16" t="n">
-        <v>17</v>
-      </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2</v>
-      </c>
       <c r="P16" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15887,7 +15887,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19015,7 +19015,7 @@
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19610,7 +19610,7 @@
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20596,7 +20596,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22347,7 +22347,7 @@
       </c>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22585,7 +22585,7 @@
       </c>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22653,7 +22653,7 @@
       </c>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22738,7 +22738,7 @@
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22806,7 +22806,7 @@
       </c>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22874,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="C1284" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23384,7 @@
       </c>
       <c r="C1299" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="C1301" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="C1324" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25560,7 +25560,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25968,7 +25968,7 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="C1457" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26274,7 +26274,7 @@
       </c>
       <c r="C1469" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C1471" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26648,7 +26648,7 @@
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26682,7 +26682,7 @@
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
